--- a/sample_templates/BOM表.xlsx
+++ b/sample_templates/BOM表.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -605,32 +605,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -642,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="115" customWidth="1" min="1" max="1"/>
@@ -689,21 +663,42 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>5. 单价（子项物料的单价）、标准成品单价：仅存档，平台核算按实际投料×月末加权价。</t>
+          <t>5. 单价（子项物料的单价）、标准成品单价：**不用填**，系统在结算后自动回填：</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6. 一个工单多子项就多行；项次按ERP原样填。</t>
+          <t xml:space="preserve">   子项单价 = 该子项物料本月月末加权平均价；</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   标准成品单价 = 按工单汇总 Σ(子项用量 × 子项单价)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6. 一个工单多子项就多行；项次按ERP原样填。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>7. 表头行必须保留在第1行；示例行（黄底）上传前请删除。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>8. 导入后可到「BOM表台账」查看系统回填的单价。</t>
         </is>
       </c>
     </row>

--- a/sample_templates/BOM表.xlsx
+++ b/sample_templates/BOM表.xlsx
@@ -434,177 +434,207 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>工单编号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>物料编号</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>物料名称</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>项次</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>子项物料编号</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>子项物料名称</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>子项用量:分子</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>子项用量:分母</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>单位名称</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>单价（子项物料的单价）</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>标准成品单价</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>BC-16.0026CS-20260720</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>BC-16.0026</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>烟台对位芳纶粗纱</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>R11.125</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>对位芳纶长丝</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>120.5</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>125</v>
-      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>11.21-20260720</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>11.21</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>对位芳纶纱线</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>BC-16.0026</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>烟台对位芳纶粗纱</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="I3" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -616,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="115" customWidth="1" min="1" max="1"/>
@@ -649,56 +679,63 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>3. 必填列：工单编号、子项物料编号；其余列可留空。</t>
+          <t>3. 序号：ERP导出的行序号，仅存档，平台不读取；可留空。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>4. 子项用量:分子 / 子项用量:分母：子项用量以分数表示（如 105/100 = 生产1单位父项消耗1.05子项）。</t>
+          <t>4. 必填列：工单编号、子项物料编号；其余列可留空。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>5. 单价（子项物料的单价）、标准成品单价：**不用填**，系统在结算后自动回填：</t>
+          <t>5. 子项用量:分子 / 子项用量:分母：子项用量以分数表示（如 105/100 = 生产1单位父项消耗1.05子项）。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   子项单价 = 该子项物料本月月末加权平均价；</t>
+          <t>6. 单价（子项物料的单价）、标准成品单价：**不用填**，系统在结算后自动回填：</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   子项单价 = 该子项物料本月月末加权平均价；</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   标准成品单价 = 按工单汇总 Σ(子项用量 × 子项单价)。</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>6. 一个工单多子项就多行；项次按ERP原样填。</t>
-        </is>
-      </c>
-    </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>7. 表头行必须保留在第1行；示例行（黄底）上传前请删除。</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>7. 一个工单多子项就多行；项次按ERP原样填。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>8. 导入后可到「BOM表台账」查看系统回填的单价。</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>8. 表头行必须保留在第1行；示例行（黄底）上传前请删除。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>9. 导入后可到「BOM表台账」查看系统回填的单价。</t>
         </is>
       </c>
     </row>

--- a/sample_templates/BOM表.xlsx
+++ b/sample_templates/BOM表.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,19 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -47,8 +58,18 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -56,17 +77,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -434,207 +476,373 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:AI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>序列</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>工单编号</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>物料编号</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>物料名称</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>项次</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>子项物料编号</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>子项物料名称</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>子项用量:分子</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>子项用量:分母</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>单位名称</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>单价（子项物料的单价）</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>标准成品单价</t>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>损耗率(%)</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>标准用量</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>需求数</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>版本号</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>需求时间</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>领料方式</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>指定供应商</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>指定批次号</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>行备注</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>指定投料工序</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>投料工序号</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>称量方案</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>获取替代方案</t>
+        </is>
+      </c>
+      <c r="Y1" s="4" t="inlineStr">
+        <is>
+          <t>默认发料仓库</t>
+        </is>
+      </c>
+      <c r="Z1" s="4" t="inlineStr">
+        <is>
+          <t>投料管控行号</t>
+        </is>
+      </c>
+      <c r="AA1" s="4" t="inlineStr">
+        <is>
+          <t>用量:分子</t>
+        </is>
+      </c>
+      <c r="AB1" s="4" t="inlineStr">
+        <is>
+          <t>投料控件编号</t>
+        </is>
+      </c>
+      <c r="AC1" s="4" t="inlineStr">
+        <is>
+          <t>是否必投</t>
+        </is>
+      </c>
+      <c r="AD1" s="4" t="inlineStr">
+        <is>
+          <t>投料上下限类型</t>
+        </is>
+      </c>
+      <c r="AE1" s="4" t="inlineStr">
+        <is>
+          <t>投料上限( 比例 % )</t>
+        </is>
+      </c>
+      <c r="AF1" s="4" t="inlineStr">
+        <is>
+          <t>投料下限( 比例 % )</t>
+        </is>
+      </c>
+      <c r="AG1" s="4" t="inlineStr">
+        <is>
+          <t>投料质量状态</t>
+        </is>
+      </c>
+      <c r="AH1" s="4" t="inlineStr">
+        <is>
+          <t>是否倒冲</t>
+        </is>
+      </c>
+      <c r="AI1" s="4" t="inlineStr">
+        <is>
+          <t>单次投料数</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>BC-16.0026CS-20260720</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>BC-16.0026</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>烟台对位芳纶粗纱</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>R11.125</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>对位芳纶长丝</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="J2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="L2" s="5" t="inlineStr"/>
+      <c r="M2" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr"/>
+      <c r="T2" s="5" t="inlineStr"/>
+      <c r="U2" s="5" t="inlineStr"/>
+      <c r="V2" s="5" t="inlineStr"/>
+      <c r="W2" s="5" t="inlineStr"/>
+      <c r="X2" s="5" t="inlineStr"/>
+      <c r="Y2" s="5" t="inlineStr"/>
+      <c r="Z2" s="5" t="inlineStr"/>
+      <c r="AA2" s="5" t="inlineStr"/>
+      <c r="AB2" s="5" t="inlineStr"/>
+      <c r="AC2" s="5" t="inlineStr"/>
+      <c r="AD2" s="5" t="inlineStr"/>
+      <c r="AE2" s="5" t="inlineStr"/>
+      <c r="AF2" s="5" t="inlineStr"/>
+      <c r="AG2" s="5" t="inlineStr"/>
+      <c r="AH2" s="5" t="inlineStr"/>
+      <c r="AI2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>11.21-20260720</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>11.21</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>对位芳纶纱线</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>BC-16.0026</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>烟台对位芳纶粗纱</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="I3" s="5" t="n">
         <v>105</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="J3" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
+      <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr"/>
+      <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr"/>
+      <c r="Z3" s="5" t="inlineStr"/>
+      <c r="AA3" s="5" t="inlineStr"/>
+      <c r="AB3" s="5" t="inlineStr"/>
+      <c r="AC3" s="5" t="inlineStr"/>
+      <c r="AD3" s="5" t="inlineStr"/>
+      <c r="AE3" s="5" t="inlineStr"/>
+      <c r="AF3" s="5" t="inlineStr"/>
+      <c r="AG3" s="5" t="inlineStr"/>
+      <c r="AH3" s="5" t="inlineStr"/>
+      <c r="AI3" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -649,11 +857,11 @@
   <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="115" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>【BOM表 填写说明】</t>
         </is>
@@ -672,72 +880,64 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2. 用途：平台按工单的BOM子项，自动识别中间品流转（粗纱等）并自动补投料，实现成本链完整。</t>
+          <t>2. 用途：平台按工单的BOM子项，自动识别中间品流转（粗纱等）并自动补投料，实现成本链完整；机织等无投料工单按 BOM 需求数反推材料成本。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>3. 序号：ERP导出的行序号，仅存档，平台不读取；可留空。</t>
+          <t>3. 必填列：工单编号、物料编号、物料名称、项次、子项物料编号、子项物料名称、子项用量:分子、子项用量:分母、单位名称；其余列可留空。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>4. 必填列：工单编号、子项物料编号；其余列可留空。</t>
+          <t>4. 序列/序号：ERP 导出的行序号，仅存档，平台不读取；可留空。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>5. 子项用量:分子 / 子项用量:分母：子项用量以分数表示（如 105/100 = 生产1单位父项消耗1.05子项）。</t>
+          <t>5. 子项用量 = 分子 ÷ 分母（千克/米 或 千克/件）。分母必须大于 0。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6. 单价（子项物料的单价）、标准成品单价：**不用填**，系统在结算后自动回填：</t>
+          <t>6. 标准用量 = 分子 ÷ 分母，可留空，系统自动计算。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   子项单价 = 该子项物料本月月末加权平均价；</t>
+          <t>7. 需求数 = 工单数量 × 标准用量 × (1+损耗率%)，该工单该子项的 BOM 需求总量（千克），建议填写。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   标准成品单价 = 按工单汇总 Σ(子项用量 × 子项单价)。</t>
+          <t>8. 损耗率(%)：填写数字，如 5 表示 5%（可选）。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>7. 一个工单多子项就多行；项次按ERP原样填。</t>
+          <t>9. 其余列（版本号/需求时间/领料方式/指定供应商/指定批次号/行备注/指定投料工序/投料工序号/称量方案/获取替代方案/默认发料仓库/投料管控行号/用量:分子/投料控件编号/是否必投/投料上下限类型/投料上限/投料下限/投料质量状态/是否倒冲/单次投料数）为 ERP 扩展信息，可留空。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>8. 表头行必须保留在第1行；示例行（黄底）上传前请删除。</t>
-        </is>
-      </c>
+      <c r="A12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>9. 导入后可到「BOM表台账」查看系统回填的单价。</t>
-        </is>
-      </c>
+      <c r="A13" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
